--- a/STUDIO/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example 1 - Bank Rating/rules/Bank Rating.xlsx
+++ b/STUDIO/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example 1 - Bank Rating/rules/Bank Rating.xlsx
@@ -2294,16 +2294,16 @@
     <t>Total Balance Score</t>
   </si>
   <si>
-    <t>&lt; 2K</t>
+    <t>&lt; 2000</t>
   </si>
   <si>
     <t>DE</t>
   </si>
   <si>
-    <t>[2K .. 30K)</t>
-  </si>
-  <si>
-    <t>&gt;= 30K</t>
+    <t>[2000 .. 30000)</t>
+  </si>
+  <si>
+    <t>&gt;= 30000</t>
   </si>
   <si>
     <t>&lt; 600</t>
@@ -2530,10 +2530,10 @@
     <t>&lt; 200</t>
   </si>
   <si>
-    <t>[200 .. 1K]</t>
-  </si>
-  <si>
-    <t>&gt; 1K</t>
+    <t>[200 .. 1000]</t>
+  </si>
+  <si>
+    <t>&gt; 1000</t>
   </si>
   <si>
     <t>Tests for "Central Bank Requirements"</t>
@@ -2762,22 +2762,22 @@
     <t>RU, UA, KZ</t>
   </si>
   <si>
-    <t>&lt; 8K</t>
-  </si>
-  <si>
-    <t>[8K .. 100K)</t>
-  </si>
-  <si>
-    <t>&gt;= 100K</t>
-  </si>
-  <si>
-    <t>&lt; 1K</t>
-  </si>
-  <si>
-    <t>[1K .. 10K)</t>
-  </si>
-  <si>
-    <t>&gt;= 10K</t>
+    <t>&lt; 8000</t>
+  </si>
+  <si>
+    <t>[8000 .. 100000)</t>
+  </si>
+  <si>
+    <t>&gt;= 100000</t>
+  </si>
+  <si>
+    <t>&lt; 1000</t>
+  </si>
+  <si>
+    <t>[1000 .. 10000)</t>
+  </si>
+  <si>
+    <t>&gt;= 10000</t>
   </si>
   <si>
     <t>Moody's Investors Service</t>
